--- a/mobile_automation/reports/Excel/Execution_Summary.xlsx
+++ b/mobile_automation/reports/Excel/Execution_Summary.xlsx
@@ -58,7 +58,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>0.03s</t>
+    <t>0.01s</t>
   </si>
   <si>
     <t>Optimal</t>
